--- a/tiflow/develop/2.0.0-ballot.2/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="178">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>43</t>
+    <t>45</t>
   </si>
   <si>
     <t>Level</t>
@@ -529,6 +529,24 @@
   </si>
   <si>
     <t>The service ran into an unspecified error.</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FLOWTYPE</t>
+  </si>
+  <si>
+    <t>FlowType Blocked</t>
+  </si>
+  <si>
+    <t>The Flowtype may not be used in the TI-Flow-Fachdienst.</t>
+  </si>
+  <si>
+    <t>TIFLOW_BLOCKED_FEATURE</t>
+  </si>
+  <si>
+    <t>Blocked Feature</t>
+  </si>
+  <si>
+    <t>The functionality for a feature is blocked in the TI-Flow-Fachdienst.</t>
   </si>
 </sst>
 </file>
@@ -840,7 +858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1459,6 +1477,34 @@
         <v>171</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/tiflow/develop/2.0.0-ballot.2/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="175">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>45</t>
+    <t>44</t>
   </si>
   <si>
     <t>Level</t>
@@ -322,15 +322,6 @@
   </si>
   <si>
     <t>The operation requires a task id in the request</t>
-  </si>
-  <si>
-    <t>TIFLOW_KVNR_MISMATCH</t>
-  </si>
-  <si>
-    <t>KVNR mismatch</t>
-  </si>
-  <si>
-    <t>The KVNR in the request does not match the KVNR assigned to the task context</t>
   </si>
   <si>
     <t>TIFLOW_SIGNATURE_INVALID</t>
@@ -858,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1491,20 +1482,6 @@
         <v>174</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
